--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11333,12 +11333,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11348,35 +11348,35 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Calgary</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>42.940498</v>
+        <v>51.113899</v>
       </c>
       <c r="H292" t="n">
-        <v>-78.732201</v>
+        <v>-114.019997</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11386,35 +11386,35 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Calgary</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>51.113899</v>
+        <v>35.214001</v>
       </c>
       <c r="H293" t="n">
-        <v>-114.019997</v>
+        <v>-80.9431</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11438,21 +11438,21 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>35.214001</v>
+        <v>41.9786</v>
       </c>
       <c r="H294" t="n">
-        <v>-80.9431</v>
+        <v>-87.90479999999999</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11476,21 +11476,21 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>41.9786</v>
+        <v>41.411701</v>
       </c>
       <c r="H295" t="n">
-        <v>-87.90479999999999</v>
+        <v>-81.8498</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -11514,21 +11514,21 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>41.411701</v>
+        <v>39.998001</v>
       </c>
       <c r="H296" t="n">
-        <v>-81.8498</v>
+        <v>-82.891899</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -11552,21 +11552,21 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>39.998001</v>
+        <v>32.896801</v>
       </c>
       <c r="H297" t="n">
-        <v>-82.891899</v>
+        <v>-97.03800200000001</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -11590,21 +11590,21 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>32.896801</v>
+        <v>39.861698</v>
       </c>
       <c r="H298" t="n">
-        <v>-97.03800200000001</v>
+        <v>-104.672997</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -11628,21 +11628,21 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>39.861698</v>
+        <v>42.212399</v>
       </c>
       <c r="H299" t="n">
-        <v>-104.672997</v>
+        <v>-83.35340100000001</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Raleigh/Durham</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>42.212399</v>
+        <v>35.877602</v>
       </c>
       <c r="H300" t="n">
-        <v>-83.35340100000001</v>
+        <v>-78.787498</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11690,35 +11690,35 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Raleigh/Durham</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>35.877602</v>
+        <v>20.521799</v>
       </c>
       <c r="H301" t="n">
-        <v>-78.787498</v>
+        <v>-103.310997</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11728,35 +11728,35 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>20.521799</v>
+        <v>44.880798</v>
       </c>
       <c r="H302" t="n">
-        <v>-103.310997</v>
+        <v>-63.508598</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11766,35 +11766,35 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>44.880798</v>
+        <v>21.318701</v>
       </c>
       <c r="H303" t="n">
-        <v>-63.508598</v>
+        <v>-157.921997</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Honolulu</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11818,21 +11818,21 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>21.318701</v>
+        <v>29.9844</v>
       </c>
       <c r="H304" t="n">
-        <v>-157.921997</v>
+        <v>-95.34139999999999</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11856,21 +11856,21 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>29.9844</v>
+        <v>39.7173</v>
       </c>
       <c r="H305" t="n">
-        <v>-95.34139999999999</v>
+        <v>-86.294403</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11894,21 +11894,21 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>39.7173</v>
+        <v>30.494101</v>
       </c>
       <c r="H306" t="n">
-        <v>-86.294403</v>
+        <v>-81.68789700000001</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11932,21 +11932,21 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>30.494101</v>
+        <v>39.2976</v>
       </c>
       <c r="H307" t="n">
-        <v>-81.68789700000001</v>
+        <v>-94.713898</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11956,35 +11956,35 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>39.2976</v>
+        <v>17.935699</v>
       </c>
       <c r="H308" t="n">
-        <v>-94.713898</v>
+        <v>-76.787498</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11994,35 +11994,35 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>17.935699</v>
+        <v>36.080101</v>
       </c>
       <c r="H309" t="n">
-        <v>-76.787498</v>
+        <v>-115.152</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -12046,21 +12046,21 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>36.080101</v>
+        <v>33.942501</v>
       </c>
       <c r="H310" t="n">
-        <v>-115.152</v>
+        <v>-118.407997</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12084,21 +12084,21 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>33.942501</v>
+        <v>35.0424</v>
       </c>
       <c r="H311" t="n">
-        <v>-118.407997</v>
+        <v>-89.97669999999999</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12108,35 +12108,35 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>35.0424</v>
+        <v>19.4363</v>
       </c>
       <c r="H312" t="n">
-        <v>-89.97669999999999</v>
+        <v>-99.072098</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12146,35 +12146,35 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>19.4363</v>
+        <v>25.7932</v>
       </c>
       <c r="H313" t="n">
-        <v>-99.072098</v>
+        <v>-80.290604</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -12198,21 +12198,21 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>25.7932</v>
+        <v>44.882</v>
       </c>
       <c r="H314" t="n">
-        <v>-80.290604</v>
+        <v>-93.221802</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12222,35 +12222,35 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>44.882</v>
+        <v>45.4706</v>
       </c>
       <c r="H315" t="n">
-        <v>-93.221802</v>
+        <v>-73.740799</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12260,35 +12260,35 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>45.4706</v>
+        <v>36.1245</v>
       </c>
       <c r="H316" t="n">
-        <v>-73.740799</v>
+        <v>-86.6782</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -12312,21 +12312,21 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>36.1245</v>
+        <v>40.692501</v>
       </c>
       <c r="H317" t="n">
-        <v>-86.6782</v>
+        <v>-74.168701</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12350,21 +12350,21 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>40.692501</v>
+        <v>36.8946</v>
       </c>
       <c r="H318" t="n">
-        <v>-74.168701</v>
+        <v>-76.20120199999999</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -12388,21 +12388,21 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>36.8946</v>
+        <v>35.393101</v>
       </c>
       <c r="H319" t="n">
-        <v>-76.20120199999999</v>
+        <v>-97.6007</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Omaha</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -12426,21 +12426,21 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>35.393101</v>
+        <v>41.3032</v>
       </c>
       <c r="H320" t="n">
-        <v>-97.6007</v>
+        <v>-95.894096</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Omaha</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12464,21 +12464,21 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>41.3032</v>
+        <v>39.871899</v>
       </c>
       <c r="H321" t="n">
-        <v>-95.894096</v>
+        <v>-75.241096</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -12502,21 +12502,21 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>39.871899</v>
+        <v>33.434299</v>
       </c>
       <c r="H322" t="n">
-        <v>-75.241096</v>
+        <v>-112.012001</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -12540,21 +12540,21 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>33.434299</v>
+        <v>40.491501</v>
       </c>
       <c r="H323" t="n">
-        <v>-112.012001</v>
+        <v>-80.23290299999999</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12578,21 +12578,21 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>40.491501</v>
+        <v>45.588699</v>
       </c>
       <c r="H324" t="n">
-        <v>-80.23290299999999</v>
+        <v>-122.598</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12602,35 +12602,35 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>45.588699</v>
+        <v>20.6173</v>
       </c>
       <c r="H325" t="n">
-        <v>-122.598</v>
+        <v>-100.185997</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12640,35 +12640,35 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>20.6173</v>
+        <v>37.505199</v>
       </c>
       <c r="H326" t="n">
-        <v>-100.185997</v>
+        <v>-77.31970200000001</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -12692,21 +12692,21 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>37.505199</v>
+        <v>38.6954</v>
       </c>
       <c r="H327" t="n">
-        <v>-77.31970200000001</v>
+        <v>-121.591003</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12730,21 +12730,21 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>38.6954</v>
+        <v>40.788399</v>
       </c>
       <c r="H328" t="n">
-        <v>-121.591003</v>
+        <v>-111.977997</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12768,21 +12768,21 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>40.788399</v>
+        <v>29.533701</v>
       </c>
       <c r="H329" t="n">
-        <v>-111.977997</v>
+        <v>-98.469803</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -12806,21 +12806,21 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>29.533701</v>
+        <v>32.733601</v>
       </c>
       <c r="H330" t="n">
-        <v>-98.469803</v>
+        <v>-117.190002</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -12844,21 +12844,21 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>32.733601</v>
+        <v>37.618999</v>
       </c>
       <c r="H331" t="n">
-        <v>-117.190002</v>
+        <v>-122.375</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>37.618999</v>
+        <v>37.362598</v>
       </c>
       <c r="H332" t="n">
-        <v>-122.375</v>
+        <v>-121.929001</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12906,35 +12906,35 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Saskatoon</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>37.362598</v>
+        <v>52.170799</v>
       </c>
       <c r="H333" t="n">
-        <v>-121.929001</v>
+        <v>-106.699997</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12944,35 +12944,35 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Saskatoon</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>52.170799</v>
+        <v>47.449001</v>
       </c>
       <c r="H334" t="n">
-        <v>-106.699997</v>
+        <v>-122.308998</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Sioux Falls</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -12996,21 +12996,21 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>47.449001</v>
+        <v>43.582001</v>
       </c>
       <c r="H335" t="n">
-        <v>-122.308998</v>
+        <v>-96.74189800000001</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Sioux Falls</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13034,21 +13034,21 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>43.582001</v>
+        <v>38.748699</v>
       </c>
       <c r="H336" t="n">
-        <v>-96.74189800000001</v>
+        <v>-90.370003</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Tallahassee</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -13072,21 +13072,21 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>38.748699</v>
+        <v>30.3965</v>
       </c>
       <c r="H337" t="n">
-        <v>-90.370003</v>
+        <v>-84.35030399999999</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Tallahassee</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -13110,21 +13110,21 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>30.3965</v>
+        <v>27.9755</v>
       </c>
       <c r="H338" t="n">
-        <v>-84.35030399999999</v>
+        <v>-82.533203</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13134,35 +13134,35 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>27.9755</v>
+        <v>43.6772</v>
       </c>
       <c r="H339" t="n">
-        <v>-82.533203</v>
+        <v>-79.6306</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -13186,21 +13186,21 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>43.6772</v>
+        <v>49.193901</v>
       </c>
       <c r="H340" t="n">
-        <v>-79.6306</v>
+        <v>-123.183998</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Winnipeg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -13224,21 +13224,21 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>49.193901</v>
+        <v>49.91</v>
       </c>
       <c r="H341" t="n">
-        <v>-123.183998</v>
+        <v>-97.23989899999999</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -13248,61 +13248,23 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Winnipeg</t>
+          <t>Hebron</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>49.91</v>
+        <v>39.048801</v>
       </c>
       <c r="H342" t="n">
-        <v>-97.23989899999999</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="inlineStr">
-        <is>
-          <t>CVG</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Cincinnati, United States</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Hebron</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G343" t="n">
-        <v>39.048801</v>
-      </c>
-      <c r="H343" t="n">
         <v>-84.667801</v>
       </c>
     </row>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7031,12 +7031,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7046,35 +7046,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>-4.38575</v>
+        <v>30.121901</v>
       </c>
       <c r="H175" t="n">
-        <v>15.4446</v>
+        <v>31.4056</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7084,35 +7084,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>30.121901</v>
+        <v>-22.4799</v>
       </c>
       <c r="H176" t="n">
-        <v>31.4056</v>
+        <v>17.4709</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7122,35 +7122,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>-22.4799</v>
+        <v>6.90317</v>
       </c>
       <c r="H177" t="n">
-        <v>17.4709</v>
+        <v>-5.36558</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7174,21 +7174,21 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>6.90317</v>
+        <v>5.26139</v>
       </c>
       <c r="H178" t="n">
-        <v>-5.36558</v>
+        <v>-3.92629</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7198,35 +7198,35 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>5.26139</v>
+        <v>0.042386</v>
       </c>
       <c r="H179" t="n">
-        <v>-3.92629</v>
+        <v>32.443501</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7236,35 +7236,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>St Denis</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.042386</v>
+        <v>-20.8871</v>
       </c>
       <c r="H180" t="n">
-        <v>32.443501</v>
+        <v>55.5103</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7274,35 +7274,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>St Denis</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Réunion</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>-20.8871</v>
+        <v>-15.3308</v>
       </c>
       <c r="H181" t="n">
-        <v>55.5103</v>
+        <v>28.4526</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7312,35 +7312,35 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>-15.3308</v>
+        <v>8.97789</v>
       </c>
       <c r="H182" t="n">
-        <v>28.4526</v>
+        <v>38.799301</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7350,35 +7350,35 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>DZ</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>8.97789</v>
+        <v>36.276001</v>
       </c>
       <c r="H183" t="n">
-        <v>38.799301</v>
+        <v>6.62039</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>DLA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Douala, Cameroon</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7388,35 +7388,35 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Douala</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>36.276001</v>
+        <v>4.00608</v>
       </c>
       <c r="H184" t="n">
-        <v>6.62039</v>
+        <v>9.719480000000001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>DLA</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Douala, Cameroon</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7426,149 +7426,149 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>4.00608</v>
+        <v>-13.7894</v>
       </c>
       <c r="H185" t="n">
-        <v>9.719480000000001</v>
+        <v>33.780998</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>-13.7894</v>
+        <v>23.0772</v>
       </c>
       <c r="H186" t="n">
-        <v>33.780998</v>
+        <v>72.634697</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>23.0772</v>
+        <v>43.3521</v>
       </c>
       <c r="H187" t="n">
-        <v>72.634697</v>
+        <v>77.040497</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>43.3521</v>
+        <v>13.1979</v>
       </c>
       <c r="H188" t="n">
-        <v>77.040497</v>
+        <v>77.706299</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7578,35 +7578,35 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>13.1979</v>
+        <v>13.6811</v>
       </c>
       <c r="H189" t="n">
-        <v>77.706299</v>
+        <v>100.747002</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7616,35 +7616,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>13.6811</v>
+        <v>4.9442</v>
       </c>
       <c r="H190" t="n">
-        <v>100.747002</v>
+        <v>114.928001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7654,35 +7654,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Lapu-Lapu City</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>4.9442</v>
+        <v>10.3075</v>
       </c>
       <c r="H191" t="n">
-        <v>114.928001</v>
+        <v>123.978996</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7692,107 +7692,107 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Lapu-Lapu City</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>10.3075</v>
+        <v>30.6735</v>
       </c>
       <c r="H192" t="n">
-        <v>123.978996</v>
+        <v>76.788498</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>30.6735</v>
-      </c>
-      <c r="H193" t="n">
-        <v>76.788498</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>12.990005</v>
+      </c>
+      <c r="H194" t="n">
+        <v>80.169296</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7802,35 +7802,35 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>12.990005</v>
+        <v>22.249599</v>
       </c>
       <c r="H195" t="n">
-        <v>80.169296</v>
+        <v>91.813301</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7840,35 +7840,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>22.249599</v>
+        <v>7.18076</v>
       </c>
       <c r="H196" t="n">
-        <v>91.813301</v>
+        <v>79.884102</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7878,145 +7878,141 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>7.18076</v>
+        <v>23.843347</v>
       </c>
       <c r="H197" t="n">
-        <v>79.884102</v>
+        <v>90.397783</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>BD</t>
-        </is>
-      </c>
-      <c r="G198" t="n">
-        <v>23.843347</v>
-      </c>
-      <c r="H198" t="n">
-        <v>90.397783</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>33.585899</v>
+      </c>
+      <c r="H199" t="n">
+        <v>130.451004</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G200" t="n">
-        <v>33.585899</v>
-      </c>
-      <c r="H200" t="n">
-        <v>130.451004</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8026,7 +8022,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8045,12 +8041,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8060,7 +8056,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8079,118 +8075,122 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Haikou, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Haikou</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>21.221201</v>
+      </c>
+      <c r="H203" t="n">
+        <v>105.806999</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>VN</t>
-        </is>
-      </c>
-      <c r="G204" t="n">
-        <v>21.221201</v>
-      </c>
-      <c r="H204" t="n">
-        <v>105.806999</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hengshui, China</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Hengshui</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>10.8188</v>
+      </c>
+      <c r="H205" t="n">
+        <v>106.652</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -8200,35 +8200,31 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>10.8188</v>
+        <v>22.308901</v>
       </c>
       <c r="H206" t="n">
-        <v>106.652</v>
+        <v>113.915001</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8238,31 +8234,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>22.308901</v>
+        <v>17.231318</v>
       </c>
       <c r="H207" t="n">
-        <v>113.915001</v>
+        <v>78.429855</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8272,35 +8272,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>17.231318</v>
+        <v>33.616699</v>
       </c>
       <c r="H208" t="n">
-        <v>78.429855</v>
+        <v>73.099197</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8310,107 +8310,107 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>33.616699</v>
+        <v>-6.12557</v>
       </c>
       <c r="H209" t="n">
-        <v>73.099197</v>
+        <v>106.655998</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="G210" t="n">
-        <v>-6.12557</v>
-      </c>
-      <c r="H210" t="n">
-        <v>106.655998</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Jinan, China</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Jinan</t>
+          <t>Senai</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>1.64131</v>
+      </c>
+      <c r="H211" t="n">
+        <v>103.669998</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8420,35 +8420,35 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Senai</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1.64131</v>
+        <v>26.399462</v>
       </c>
       <c r="H212" t="n">
-        <v>103.669998</v>
+        <v>80.42695000000001</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8458,35 +8458,31 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+          <t>Kaohsiung City</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>26.399462</v>
+        <v>22.577101</v>
       </c>
       <c r="H213" t="n">
-        <v>80.42695000000001</v>
+        <v>120.349998</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8496,31 +8492,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>22.577101</v>
+        <v>24.9065</v>
       </c>
       <c r="H214" t="n">
-        <v>120.349998</v>
+        <v>67.160797</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8530,35 +8530,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>24.9065</v>
+        <v>27.6966</v>
       </c>
       <c r="H215" t="n">
-        <v>67.160797</v>
+        <v>85.3591</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8568,35 +8568,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>27.6966</v>
+        <v>22.654699</v>
       </c>
       <c r="H216" t="n">
-        <v>85.3591</v>
+        <v>88.446701</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8606,107 +8606,103 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>22.654699</v>
+        <v>2.74558</v>
       </c>
       <c r="H217" t="n">
-        <v>88.446701</v>
+        <v>101.709999</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Langfang</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="G218" t="n">
-        <v>2.74558</v>
-      </c>
-      <c r="H218" t="n">
-        <v>101.709999</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Langfang</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
+          <t>Taipa</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>22.149599</v>
+      </c>
+      <c r="H219" t="n">
+        <v>113.592003</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8716,31 +8712,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Taipa</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MV</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>22.149599</v>
+        <v>4.19183</v>
       </c>
       <c r="H220" t="n">
-        <v>113.592003</v>
+        <v>73.529099</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8750,35 +8750,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>4.19183</v>
+        <v>14.5086</v>
       </c>
       <c r="H221" t="n">
-        <v>73.529099</v>
+        <v>121.019997</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8788,35 +8788,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>14.5086</v>
+        <v>19.088699</v>
       </c>
       <c r="H222" t="n">
-        <v>121.019997</v>
+        <v>72.867897</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Naqpur</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8840,21 +8840,21 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>19.088699</v>
+        <v>21.092199</v>
       </c>
       <c r="H223" t="n">
-        <v>72.867897</v>
+        <v>79.047203</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8864,35 +8864,35 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Naqpur</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>21.092199</v>
+        <v>26.195801</v>
       </c>
       <c r="H224" t="n">
-        <v>79.047203</v>
+        <v>127.646004</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8902,35 +8902,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>26.195801</v>
+        <v>28.5665</v>
       </c>
       <c r="H225" t="n">
-        <v>127.646004</v>
+        <v>77.103104</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8940,35 +8940,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>28.5665</v>
+        <v>34.427299</v>
       </c>
       <c r="H226" t="n">
-        <v>77.103104</v>
+        <v>135.244003</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8978,35 +8978,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>34.427299</v>
+        <v>25.591299</v>
       </c>
       <c r="H227" t="n">
-        <v>135.244003</v>
+        <v>85.087997</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9016,179 +9016,179 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>25.591299</v>
+        <v>11.5466</v>
       </c>
       <c r="H228" t="n">
-        <v>85.087997</v>
+        <v>104.844002</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="G229" t="n">
-        <v>11.5466</v>
-      </c>
-      <c r="H229" t="n">
-        <v>104.844002</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>37.469101</v>
+      </c>
+      <c r="H230" t="n">
+        <v>126.450996</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G231" t="n">
-        <v>37.469101</v>
-      </c>
-      <c r="H231" t="n">
-        <v>126.450996</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1.35019</v>
+      </c>
+      <c r="H232" t="n">
+        <v>103.994003</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9198,35 +9198,35 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Surat Thani</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.35019</v>
+        <v>9.1326</v>
       </c>
       <c r="H233" t="n">
-        <v>103.994003</v>
+        <v>99.135597</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9236,35 +9236,31 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>9.1326</v>
+        <v>25.0777</v>
       </c>
       <c r="H234" t="n">
-        <v>99.135597</v>
+        <v>121.233002</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9274,31 +9270,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>25.0777</v>
+        <v>35.764702</v>
       </c>
       <c r="H235" t="n">
-        <v>121.233002</v>
+        <v>140.386002</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9308,35 +9308,35 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ulan Bator</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>35.764702</v>
+        <v>47.843102</v>
       </c>
       <c r="H236" t="n">
-        <v>140.386002</v>
+        <v>106.766998</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9346,145 +9346,145 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ulan Bator</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>47.843102</v>
+        <v>17.9883</v>
       </c>
       <c r="H237" t="n">
-        <v>106.766998</v>
+        <v>102.563004</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
-        <v>17.9883</v>
-      </c>
-      <c r="H238" t="n">
-        <v>102.563004</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>40.147301</v>
+      </c>
+      <c r="H239" t="n">
+        <v>44.395901</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Yogyakarta-Java Island</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>40.147301</v>
+        <v>-7.78818</v>
       </c>
       <c r="H240" t="n">
-        <v>44.395901</v>
+        <v>110.431999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9494,35 +9494,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yogyakarta-Java Island</t>
+          <t>Cagayan De Oro City</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>-7.78818</v>
+        <v>8.415620000000001</v>
       </c>
       <c r="H241" t="n">
-        <v>110.431999</v>
+        <v>124.611</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9532,35 +9532,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cagayan De Oro City</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>8.415620000000001</v>
+        <v>10.152</v>
       </c>
       <c r="H242" t="n">
-        <v>124.611</v>
+        <v>76.401901</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9570,35 +9570,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>Denpasar-Bali Island</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>10.152</v>
+        <v>-8.74817</v>
       </c>
       <c r="H243" t="n">
-        <v>76.401901</v>
+        <v>115.167</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9608,73 +9608,69 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Denpasar-Bali Island</t>
+          <t>Mattanur</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>-8.74817</v>
+        <v>11.92</v>
       </c>
       <c r="H244" t="n">
-        <v>115.167</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Mattanur</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G245" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="H245" t="n">
-        <v>75.55</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9684,7 +9680,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9703,12 +9699,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9718,7 +9714,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9737,12 +9733,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9752,7 +9748,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9771,12 +9767,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9786,7 +9782,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9805,84 +9801,84 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>18.7668</v>
+      </c>
+      <c r="H250" t="n">
+        <v>98.96260100000001</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="G251" t="n">
-        <v>18.7668</v>
-      </c>
-      <c r="H251" t="n">
-        <v>98.96260100000001</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9892,7 +9888,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9911,12 +9907,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9926,7 +9922,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9945,12 +9941,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9960,7 +9956,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9979,12 +9975,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9994,7 +9990,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -10013,12 +10009,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10028,7 +10024,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10047,118 +10043,122 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>16.0439</v>
+      </c>
+      <c r="H257" t="n">
+        <v>108.198997</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>VN</t>
-        </is>
-      </c>
-      <c r="G258" t="n">
-        <v>16.0439</v>
-      </c>
-      <c r="H258" t="n">
-        <v>108.198997</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Mabalacat</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>15.186</v>
+      </c>
+      <c r="H259" t="n">
+        <v>120.559998</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10168,183 +10168,179 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Mabalacat</t>
+          <t>Paro</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>15.186</v>
+        <v>27.4032</v>
       </c>
       <c r="H260" t="n">
-        <v>120.559998</v>
+        <v>89.424599</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Paro</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="G261" t="n">
-        <v>27.4032</v>
-      </c>
-      <c r="H261" t="n">
-        <v>89.424599</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1.4847</v>
+      </c>
+      <c r="H262" t="n">
+        <v>110.347</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Aktyubinsk</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>1.4847</v>
+        <v>50.2458</v>
       </c>
       <c r="H263" t="n">
-        <v>110.347</v>
+        <v>57.206699</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Aktyubinsk</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
-        <v>50.2458</v>
-      </c>
-      <c r="H264" t="n">
-        <v>57.206699</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10354,7 +10350,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -10373,46 +10369,50 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>43.061272</v>
+      </c>
+      <c r="H266" t="n">
+        <v>74.477508</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10422,35 +10422,35 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Malang-Java Island</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>43.061272</v>
+        <v>-7.92656</v>
       </c>
       <c r="H267" t="n">
-        <v>74.477508</v>
+        <v>112.714996</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10460,107 +10460,103 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Malang-Java Island</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>-7.92656</v>
+        <v>31.521601</v>
       </c>
       <c r="H268" t="n">
-        <v>112.714996</v>
+        <v>74.403603</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G269" t="n">
-        <v>31.521601</v>
-      </c>
-      <c r="H269" t="n">
-        <v>74.403603</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Chengdu</t>
-        </is>
-      </c>
+          <t>Asia Pacific</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>27.1558</v>
+      </c>
+      <c r="H270" t="n">
+        <v>77.960899</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10568,7 +10564,11 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>India</t>
@@ -10580,165 +10580,165 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>27.1558</v>
+        <v>11.03</v>
       </c>
       <c r="H271" t="n">
-        <v>77.960899</v>
+        <v>77.043404</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G272" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="H272" t="n">
-        <v>77.043404</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>20.2444</v>
+      </c>
+      <c r="H273" t="n">
+        <v>85.817802</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G274" t="n">
-        <v>20.2444</v>
-      </c>
-      <c r="H274" t="n">
-        <v>85.817802</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>18.5821</v>
+      </c>
+      <c r="H275" t="n">
+        <v>73.919701</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Jharsuguda</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10762,93 +10762,93 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>18.5821</v>
+        <v>21.9135</v>
       </c>
       <c r="H276" t="n">
-        <v>73.919701</v>
+        <v>84.0504</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>JRG</t>
+          <t>AVA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Sambalpur, India</t>
+          <t>Anshun, China</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Jharsuguda</t>
+          <t>Anshun</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G277" t="n">
-        <v>21.9135</v>
-      </c>
-      <c r="H277" t="n">
-        <v>84.0504</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>AVA</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Anshun, China</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Anshun</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>51.022202</v>
+      </c>
+      <c r="H278" t="n">
+        <v>71.466904</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>BDQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Jamnagar, India</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10858,35 +10858,35 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>51.022202</v>
+        <v>22.336201</v>
       </c>
       <c r="H279" t="n">
-        <v>71.466904</v>
+        <v>73.226303</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>BDQ</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Jamnagar, India</t>
+          <t>Udaipur, India</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>22.336201</v>
+        <v>24.617701</v>
       </c>
       <c r="H280" t="n">
-        <v>73.226303</v>
+        <v>73.896103</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>AIP</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Udaipur, India</t>
+          <t>Jalandhar, India</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10932,11 +10932,7 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Udaipur</t>
-        </is>
-      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>India</t>
@@ -10948,89 +10944,93 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>24.617701</v>
+        <v>31.4338</v>
       </c>
       <c r="H281" t="n">
-        <v>73.896103</v>
+        <v>75.758797</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>LHW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Jalandhar, India</t>
+          <t>Lanzhou, China</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Lanzhou</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G282" t="n">
-        <v>31.4338</v>
-      </c>
-      <c r="H282" t="n">
-        <v>75.758797</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>LHW</t>
+          <t>DYU</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Lanzhou, China</t>
+          <t>Dushanbe, Tajikistan</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Lanzhou</t>
+          <t>Dushanbe</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>38.543301</v>
+      </c>
+      <c r="H283" t="n">
+        <v>68.824997</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>DYU</t>
+          <t>LUH</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dushanbe, Tajikistan</t>
+          <t>Ludhiana, India</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11038,71 +11038,71 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Dushanbe</t>
-        </is>
-      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>38.543301</v>
+        <v>30.8547</v>
       </c>
       <c r="H284" t="n">
-        <v>68.824997</v>
+        <v>75.95259900000001</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>LUH</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ludhiana, India</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Albuquerque</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>30.8547</v>
+        <v>35.040199</v>
       </c>
       <c r="H285" t="n">
-        <v>75.95259900000001</v>
+        <v>-106.609001</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Albuquerque</t>
+          <t>Anchorage</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11126,21 +11126,21 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>35.040199</v>
+        <v>61.1744</v>
       </c>
       <c r="H286" t="n">
-        <v>-106.609001</v>
+        <v>-149.996002</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Anchorage</t>
+          <t>Dulles</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11164,21 +11164,21 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>61.1744</v>
+        <v>38.9445</v>
       </c>
       <c r="H287" t="n">
-        <v>-149.996002</v>
+        <v>-77.455803</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Dulles</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11202,21 +11202,21 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>38.9445</v>
+        <v>33.6367</v>
       </c>
       <c r="H288" t="n">
-        <v>-77.455803</v>
+        <v>-84.428101</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11240,21 +11240,21 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>33.6367</v>
+        <v>30.1945</v>
       </c>
       <c r="H289" t="n">
-        <v>-84.428101</v>
+        <v>-97.669899</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11278,21 +11278,21 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>30.1945</v>
+        <v>44.8074</v>
       </c>
       <c r="H290" t="n">
-        <v>-97.669899</v>
+        <v>-68.828102</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11316,21 +11316,21 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>44.8074</v>
+        <v>42.3643</v>
       </c>
       <c r="H291" t="n">
-        <v>-68.828102</v>
+        <v>-71.00520299999999</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11340,35 +11340,35 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Calgary</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>42.3643</v>
+        <v>51.113899</v>
       </c>
       <c r="H292" t="n">
-        <v>-71.00520299999999</v>
+        <v>-114.019997</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11378,35 +11378,35 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Calgary</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>51.113899</v>
+        <v>35.214001</v>
       </c>
       <c r="H293" t="n">
-        <v>-114.019997</v>
+        <v>-80.9431</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11430,21 +11430,21 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>35.214001</v>
+        <v>41.9786</v>
       </c>
       <c r="H294" t="n">
-        <v>-80.9431</v>
+        <v>-87.90479999999999</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11468,21 +11468,21 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>41.9786</v>
+        <v>41.411701</v>
       </c>
       <c r="H295" t="n">
-        <v>-87.90479999999999</v>
+        <v>-81.8498</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -11506,21 +11506,21 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>41.411701</v>
+        <v>39.998001</v>
       </c>
       <c r="H296" t="n">
-        <v>-81.8498</v>
+        <v>-82.891899</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -11544,21 +11544,21 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>39.998001</v>
+        <v>32.896801</v>
       </c>
       <c r="H297" t="n">
-        <v>-82.891899</v>
+        <v>-97.03800200000001</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -11582,21 +11582,21 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>32.896801</v>
+        <v>39.861698</v>
       </c>
       <c r="H298" t="n">
-        <v>-97.03800200000001</v>
+        <v>-104.672997</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -11620,21 +11620,21 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>39.861698</v>
+        <v>42.212399</v>
       </c>
       <c r="H299" t="n">
-        <v>-104.672997</v>
+        <v>-83.35340100000001</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Raleigh/Durham</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11658,21 +11658,21 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>42.212399</v>
+        <v>35.877602</v>
       </c>
       <c r="H300" t="n">
-        <v>-83.35340100000001</v>
+        <v>-78.787498</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11682,35 +11682,35 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Raleigh/Durham</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>35.877602</v>
+        <v>20.521799</v>
       </c>
       <c r="H301" t="n">
-        <v>-78.787498</v>
+        <v>-103.310997</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11720,35 +11720,35 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>20.521799</v>
+        <v>44.880798</v>
       </c>
       <c r="H302" t="n">
-        <v>-103.310997</v>
+        <v>-63.508598</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11758,35 +11758,35 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>44.880798</v>
+        <v>21.318701</v>
       </c>
       <c r="H303" t="n">
-        <v>-63.508598</v>
+        <v>-157.921997</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Honolulu</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11810,21 +11810,21 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>21.318701</v>
+        <v>29.9844</v>
       </c>
       <c r="H304" t="n">
-        <v>-157.921997</v>
+        <v>-95.34139999999999</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11848,21 +11848,21 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>29.9844</v>
+        <v>39.7173</v>
       </c>
       <c r="H305" t="n">
-        <v>-95.34139999999999</v>
+        <v>-86.294403</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>39.7173</v>
+        <v>30.494101</v>
       </c>
       <c r="H306" t="n">
-        <v>-86.294403</v>
+        <v>-81.68789700000001</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11924,21 +11924,21 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>30.494101</v>
+        <v>39.2976</v>
       </c>
       <c r="H307" t="n">
-        <v>-81.68789700000001</v>
+        <v>-94.713898</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11948,35 +11948,35 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>39.2976</v>
+        <v>17.935699</v>
       </c>
       <c r="H308" t="n">
-        <v>-94.713898</v>
+        <v>-76.787498</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11986,35 +11986,35 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>17.935699</v>
+        <v>36.080101</v>
       </c>
       <c r="H309" t="n">
-        <v>-76.787498</v>
+        <v>-115.152</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -12038,21 +12038,21 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>36.080101</v>
+        <v>33.942501</v>
       </c>
       <c r="H310" t="n">
-        <v>-115.152</v>
+        <v>-118.407997</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12076,21 +12076,21 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>33.942501</v>
+        <v>35.0424</v>
       </c>
       <c r="H311" t="n">
-        <v>-118.407997</v>
+        <v>-89.97669999999999</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12100,35 +12100,35 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>35.0424</v>
+        <v>19.4363</v>
       </c>
       <c r="H312" t="n">
-        <v>-89.97669999999999</v>
+        <v>-99.072098</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12138,35 +12138,35 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>19.4363</v>
+        <v>25.7932</v>
       </c>
       <c r="H313" t="n">
-        <v>-99.072098</v>
+        <v>-80.290604</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -12190,21 +12190,21 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>25.7932</v>
+        <v>44.882</v>
       </c>
       <c r="H314" t="n">
-        <v>-80.290604</v>
+        <v>-93.221802</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12214,35 +12214,35 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>44.882</v>
+        <v>45.4706</v>
       </c>
       <c r="H315" t="n">
-        <v>-93.221802</v>
+        <v>-73.740799</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12252,35 +12252,35 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>45.4706</v>
+        <v>36.1245</v>
       </c>
       <c r="H316" t="n">
-        <v>-73.740799</v>
+        <v>-86.6782</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -12304,21 +12304,21 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>36.1245</v>
+        <v>40.692501</v>
       </c>
       <c r="H317" t="n">
-        <v>-86.6782</v>
+        <v>-74.168701</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12342,21 +12342,21 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>40.692501</v>
+        <v>36.8946</v>
       </c>
       <c r="H318" t="n">
-        <v>-74.168701</v>
+        <v>-76.20120199999999</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -12380,21 +12380,21 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>36.8946</v>
+        <v>35.393101</v>
       </c>
       <c r="H319" t="n">
-        <v>-76.20120199999999</v>
+        <v>-97.6007</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Omaha</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -12418,21 +12418,21 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>35.393101</v>
+        <v>41.3032</v>
       </c>
       <c r="H320" t="n">
-        <v>-97.6007</v>
+        <v>-95.894096</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Omaha</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>41.3032</v>
+        <v>39.871899</v>
       </c>
       <c r="H321" t="n">
-        <v>-95.894096</v>
+        <v>-75.241096</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -12494,21 +12494,21 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>39.871899</v>
+        <v>33.434299</v>
       </c>
       <c r="H322" t="n">
-        <v>-75.241096</v>
+        <v>-112.012001</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>33.434299</v>
+        <v>40.491501</v>
       </c>
       <c r="H323" t="n">
-        <v>-112.012001</v>
+        <v>-80.23290299999999</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12570,21 +12570,21 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>40.491501</v>
+        <v>45.588699</v>
       </c>
       <c r="H324" t="n">
-        <v>-80.23290299999999</v>
+        <v>-122.598</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12594,35 +12594,35 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>45.588699</v>
+        <v>20.6173</v>
       </c>
       <c r="H325" t="n">
-        <v>-122.598</v>
+        <v>-100.185997</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12632,35 +12632,35 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>20.6173</v>
+        <v>37.505199</v>
       </c>
       <c r="H326" t="n">
-        <v>-100.185997</v>
+        <v>-77.31970200000001</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -12684,21 +12684,21 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>37.505199</v>
+        <v>38.6954</v>
       </c>
       <c r="H327" t="n">
-        <v>-77.31970200000001</v>
+        <v>-121.591003</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12722,21 +12722,21 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>38.6954</v>
+        <v>40.788399</v>
       </c>
       <c r="H328" t="n">
-        <v>-121.591003</v>
+        <v>-111.977997</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12760,21 +12760,21 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>40.788399</v>
+        <v>29.533701</v>
       </c>
       <c r="H329" t="n">
-        <v>-111.977997</v>
+        <v>-98.469803</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>29.533701</v>
+        <v>32.733601</v>
       </c>
       <c r="H330" t="n">
-        <v>-98.469803</v>
+        <v>-117.190002</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>32.733601</v>
+        <v>37.618999</v>
       </c>
       <c r="H331" t="n">
-        <v>-117.190002</v>
+        <v>-122.375</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>37.618999</v>
+        <v>37.362598</v>
       </c>
       <c r="H332" t="n">
-        <v>-122.375</v>
+        <v>-121.929001</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12898,35 +12898,35 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Saskatoon</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>37.362598</v>
+        <v>52.170799</v>
       </c>
       <c r="H333" t="n">
-        <v>-121.929001</v>
+        <v>-106.699997</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12936,35 +12936,35 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Saskatoon</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>52.170799</v>
+        <v>47.449001</v>
       </c>
       <c r="H334" t="n">
-        <v>-106.699997</v>
+        <v>-122.308998</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Sioux Falls</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -12988,21 +12988,21 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>47.449001</v>
+        <v>43.582001</v>
       </c>
       <c r="H335" t="n">
-        <v>-122.308998</v>
+        <v>-96.74189800000001</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Sioux Falls</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13026,21 +13026,21 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>43.582001</v>
+        <v>38.748699</v>
       </c>
       <c r="H336" t="n">
-        <v>-96.74189800000001</v>
+        <v>-90.370003</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Tallahassee</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -13064,21 +13064,21 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>38.748699</v>
+        <v>30.3965</v>
       </c>
       <c r="H337" t="n">
-        <v>-90.370003</v>
+        <v>-84.35030399999999</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Tallahassee</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -13102,21 +13102,21 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>30.3965</v>
+        <v>27.9755</v>
       </c>
       <c r="H338" t="n">
-        <v>-84.35030399999999</v>
+        <v>-82.533203</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13126,35 +13126,35 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>27.9755</v>
+        <v>43.6772</v>
       </c>
       <c r="H339" t="n">
-        <v>-82.533203</v>
+        <v>-79.6306</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>43.6772</v>
+        <v>49.193901</v>
       </c>
       <c r="H340" t="n">
-        <v>-79.6306</v>
+        <v>-123.183998</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Winnipeg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -13216,21 +13216,21 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>49.193901</v>
+        <v>49.91</v>
       </c>
       <c r="H341" t="n">
-        <v>-123.183998</v>
+        <v>-97.23989899999999</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -13240,61 +13240,23 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Winnipeg</t>
+          <t>Hebron</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>49.91</v>
+        <v>39.048801</v>
       </c>
       <c r="H342" t="n">
-        <v>-97.23989899999999</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="inlineStr">
-        <is>
-          <t>CVG</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Cincinnati, United States</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Hebron</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G343" t="n">
-        <v>39.048801</v>
-      </c>
-      <c r="H343" t="n">
         <v>-84.667801</v>
       </c>
     </row>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H342"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,50 +10869,50 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>JAI</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Albuquerque, United States</t>
+          <t>“Jaipur”, India</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Albuquerque</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>35.040199</v>
+        <v>26.8242</v>
       </c>
       <c r="H280" t="n">
-        <v>-106.609001</v>
+        <v>75.812202</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Anchorage, United States</t>
+          <t>Albuquerque, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Anchorage</t>
+          <t>Albuquerque</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -10936,21 +10936,21 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>61.1744</v>
+        <v>35.040199</v>
       </c>
       <c r="H281" t="n">
-        <v>-149.996002</v>
+        <v>-106.609001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ashburn, United States</t>
+          <t>Anchorage, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Dulles</t>
+          <t>Anchorage</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10974,21 +10974,21 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>38.9445</v>
+        <v>61.1744</v>
       </c>
       <c r="H282" t="n">
-        <v>-77.455803</v>
+        <v>-149.996002</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Atlanta, United States</t>
+          <t>Ashburn, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Dulles</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11012,21 +11012,21 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>33.6367</v>
+        <v>38.9445</v>
       </c>
       <c r="H283" t="n">
-        <v>-84.428101</v>
+        <v>-77.455803</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Austin, United States</t>
+          <t>Atlanta, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11050,21 +11050,21 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>30.1945</v>
+        <v>33.6367</v>
       </c>
       <c r="H284" t="n">
-        <v>-97.669899</v>
+        <v>-84.428101</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bangor, United States</t>
+          <t>Austin, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11088,21 +11088,21 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>44.8074</v>
+        <v>30.1945</v>
       </c>
       <c r="H285" t="n">
-        <v>-68.828102</v>
+        <v>-97.669899</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Boston, United States</t>
+          <t>Bangor, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11126,21 +11126,21 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>42.3643</v>
+        <v>44.8074</v>
       </c>
       <c r="H286" t="n">
-        <v>-71.00520299999999</v>
+        <v>-68.828102</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>Boston, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11150,35 +11150,35 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Calgary</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>51.113899</v>
+        <v>42.3643</v>
       </c>
       <c r="H287" t="n">
-        <v>-114.019997</v>
+        <v>-71.00520299999999</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Charlotte, United States</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11188,35 +11188,35 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Calgary</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>35.214001</v>
+        <v>51.113899</v>
       </c>
       <c r="H288" t="n">
-        <v>-80.9431</v>
+        <v>-114.019997</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Chicago, United States</t>
+          <t>Charlotte, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11240,21 +11240,21 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>41.9786</v>
+        <v>35.214001</v>
       </c>
       <c r="H289" t="n">
-        <v>-87.90479999999999</v>
+        <v>-80.9431</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cleveland, United States</t>
+          <t>Chicago, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11278,21 +11278,21 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>41.411701</v>
+        <v>41.9786</v>
       </c>
       <c r="H290" t="n">
-        <v>-81.8498</v>
+        <v>-87.90479999999999</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Columbus, United States</t>
+          <t>Cleveland, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11316,21 +11316,21 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>39.998001</v>
+        <v>41.411701</v>
       </c>
       <c r="H291" t="n">
-        <v>-82.891899</v>
+        <v>-81.8498</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Dallas, United States</t>
+          <t>Columbus, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11354,21 +11354,21 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>32.896801</v>
+        <v>39.998001</v>
       </c>
       <c r="H292" t="n">
-        <v>-97.03800200000001</v>
+        <v>-82.891899</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Denver, United States</t>
+          <t>Dallas, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -11392,21 +11392,21 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>39.861698</v>
+        <v>32.896801</v>
       </c>
       <c r="H293" t="n">
-        <v>-104.672997</v>
+        <v>-97.03800200000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Detroit, United States</t>
+          <t>Denver, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11430,21 +11430,21 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>42.212399</v>
+        <v>39.861698</v>
       </c>
       <c r="H294" t="n">
-        <v>-83.35340100000001</v>
+        <v>-104.672997</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Durham, United States</t>
+          <t>Detroit, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Raleigh/Durham</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11468,21 +11468,21 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>35.877602</v>
+        <v>42.212399</v>
       </c>
       <c r="H295" t="n">
-        <v>-78.787498</v>
+        <v>-83.35340100000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11492,35 +11492,35 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Raleigh/Durham</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>20.521799</v>
+        <v>35.877602</v>
       </c>
       <c r="H296" t="n">
-        <v>-103.310997</v>
+        <v>-78.787498</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11530,35 +11530,35 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>44.880798</v>
+        <v>20.521799</v>
       </c>
       <c r="H297" t="n">
-        <v>-63.508598</v>
+        <v>-103.310997</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11568,35 +11568,35 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>14.5833</v>
+        <v>44.880798</v>
       </c>
       <c r="H298" t="n">
-        <v>-90.527496</v>
+        <v>-63.508598</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Honolulu, United States</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11606,35 +11606,35 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Honolulu</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>21.318701</v>
+        <v>14.5833</v>
       </c>
       <c r="H299" t="n">
-        <v>-157.921997</v>
+        <v>-90.527496</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Houston, United States</t>
+          <t>Honolulu, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11658,21 +11658,21 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>29.9844</v>
+        <v>21.318701</v>
       </c>
       <c r="H300" t="n">
-        <v>-95.34139999999999</v>
+        <v>-157.921997</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Indianapolis, United States</t>
+          <t>Houston, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -11696,21 +11696,21 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>39.7173</v>
+        <v>29.9844</v>
       </c>
       <c r="H301" t="n">
-        <v>-86.294403</v>
+        <v>-95.34139999999999</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Jacksonville, United States</t>
+          <t>Indianapolis, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -11734,21 +11734,21 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>30.494101</v>
+        <v>39.7173</v>
       </c>
       <c r="H302" t="n">
-        <v>-81.68789700000001</v>
+        <v>-86.294403</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kansas City, United States</t>
+          <t>Jacksonville, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -11772,21 +11772,21 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>39.2976</v>
+        <v>30.494101</v>
       </c>
       <c r="H303" t="n">
-        <v>-94.713898</v>
+        <v>-81.68789700000001</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11796,35 +11796,35 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>17.935699</v>
+        <v>39.2976</v>
       </c>
       <c r="H304" t="n">
-        <v>-76.787498</v>
+        <v>-94.713898</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Las Vegas, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11834,35 +11834,35 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>36.080101</v>
+        <v>17.935699</v>
       </c>
       <c r="H305" t="n">
-        <v>-115.152</v>
+        <v>-76.787498</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Los Angeles, United States</t>
+          <t>Las Vegas, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>33.942501</v>
+        <v>36.080101</v>
       </c>
       <c r="H306" t="n">
-        <v>-118.407997</v>
+        <v>-115.152</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Memphis, United States</t>
+          <t>Los Angeles, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11924,21 +11924,21 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>35.0424</v>
+        <v>33.942501</v>
       </c>
       <c r="H307" t="n">
-        <v>-89.97669999999999</v>
+        <v>-118.407997</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11948,35 +11948,35 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>19.4363</v>
+        <v>35.0424</v>
       </c>
       <c r="H308" t="n">
-        <v>-99.072098</v>
+        <v>-89.97669999999999</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Miami, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11986,35 +11986,35 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>25.7932</v>
+        <v>19.4363</v>
       </c>
       <c r="H309" t="n">
-        <v>-80.290604</v>
+        <v>-99.072098</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Minneapolis, United States</t>
+          <t>Miami, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -12038,21 +12038,21 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>44.882</v>
+        <v>25.7932</v>
       </c>
       <c r="H310" t="n">
-        <v>-93.221802</v>
+        <v>-80.290604</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Montréal, Canada</t>
+          <t>Minneapolis, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12062,35 +12062,35 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>45.4706</v>
+        <v>44.882</v>
       </c>
       <c r="H311" t="n">
-        <v>-73.740799</v>
+        <v>-93.221802</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, Canada</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12100,35 +12100,35 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>36.1245</v>
+        <v>45.4706</v>
       </c>
       <c r="H312" t="n">
-        <v>-86.6782</v>
+        <v>-73.740799</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Newark, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -12152,21 +12152,21 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>40.692501</v>
+        <v>36.1245</v>
       </c>
       <c r="H313" t="n">
-        <v>-74.168701</v>
+        <v>-86.6782</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Norfolk, United States</t>
+          <t>Newark, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -12190,21 +12190,21 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>36.8946</v>
+        <v>40.692501</v>
       </c>
       <c r="H314" t="n">
-        <v>-76.20120199999999</v>
+        <v>-74.168701</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oklahoma City, United States</t>
+          <t>Norfolk, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12228,21 +12228,21 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>35.393101</v>
+        <v>36.8946</v>
       </c>
       <c r="H315" t="n">
-        <v>-97.6007</v>
+        <v>-76.20120199999999</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Omaha, United States</t>
+          <t>Oklahoma City, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Omaha</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -12266,21 +12266,21 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>41.3032</v>
+        <v>35.393101</v>
       </c>
       <c r="H316" t="n">
-        <v>-95.894096</v>
+        <v>-97.6007</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Omaha, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Omaha</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -12304,21 +12304,21 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>39.871899</v>
+        <v>41.3032</v>
       </c>
       <c r="H317" t="n">
-        <v>-75.241096</v>
+        <v>-95.894096</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Phoenix, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12342,21 +12342,21 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>33.434299</v>
+        <v>39.871899</v>
       </c>
       <c r="H318" t="n">
-        <v>-112.012001</v>
+        <v>-75.241096</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>Phoenix, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12366,35 +12366,35 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>18.429701</v>
+        <v>33.434299</v>
       </c>
       <c r="H319" t="n">
-        <v>-69.66889999999999</v>
+        <v>-112.012001</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pittsburgh, United States</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12404,35 +12404,35 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>40.491501</v>
+        <v>18.429701</v>
       </c>
       <c r="H320" t="n">
-        <v>-80.23290299999999</v>
+        <v>-69.66889999999999</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Portland, United States</t>
+          <t>Pittsburgh, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>45.588699</v>
+        <v>40.491501</v>
       </c>
       <c r="H321" t="n">
-        <v>-122.598</v>
+        <v>-80.23290299999999</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Queretaro, Mexico</t>
+          <t>Portland, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12480,35 +12480,35 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>20.6173</v>
+        <v>45.588699</v>
       </c>
       <c r="H322" t="n">
-        <v>-100.185997</v>
+        <v>-122.598</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Richmond, United States</t>
+          <t>Queretaro, Mexico</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12518,35 +12518,35 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>37.505199</v>
+        <v>20.6173</v>
       </c>
       <c r="H323" t="n">
-        <v>-77.31970200000001</v>
+        <v>-100.185997</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sacramento, United States</t>
+          <t>Richmond, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12570,21 +12570,21 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>38.6954</v>
+        <v>37.505199</v>
       </c>
       <c r="H324" t="n">
-        <v>-121.591003</v>
+        <v>-77.31970200000001</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Salt Lake City, United States</t>
+          <t>Sacramento, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -12608,21 +12608,21 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>40.788399</v>
+        <v>38.6954</v>
       </c>
       <c r="H325" t="n">
-        <v>-111.977997</v>
+        <v>-121.591003</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Antonio, United States</t>
+          <t>Salt Lake City, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -12646,21 +12646,21 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>29.533701</v>
+        <v>40.788399</v>
       </c>
       <c r="H326" t="n">
-        <v>-98.469803</v>
+        <v>-111.977997</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Diego, United States</t>
+          <t>San Antonio, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -12684,21 +12684,21 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>32.733601</v>
+        <v>29.533701</v>
       </c>
       <c r="H327" t="n">
-        <v>-117.190002</v>
+        <v>-98.469803</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Francisco, United States</t>
+          <t>San Diego, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12722,21 +12722,21 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>37.618999</v>
+        <v>32.733601</v>
       </c>
       <c r="H328" t="n">
-        <v>-122.375</v>
+        <v>-117.190002</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>San Jose, United States</t>
+          <t>San Francisco, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12760,21 +12760,21 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>37.362598</v>
+        <v>37.618999</v>
       </c>
       <c r="H329" t="n">
-        <v>-121.929001</v>
+        <v>-122.375</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Saskatoon, Canada</t>
+          <t>San Jose, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12784,35 +12784,35 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Saskatoon</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>52.170799</v>
+        <v>37.362598</v>
       </c>
       <c r="H330" t="n">
-        <v>-106.699997</v>
+        <v>-121.929001</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Seattle, United States</t>
+          <t>Saskatoon, Canada</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12822,35 +12822,35 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Saskatoon</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>47.449001</v>
+        <v>52.170799</v>
       </c>
       <c r="H331" t="n">
-        <v>-122.308998</v>
+        <v>-106.699997</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sioux Falls, United States</t>
+          <t>Seattle, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Sioux Falls</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>43.582001</v>
+        <v>47.449001</v>
       </c>
       <c r="H332" t="n">
-        <v>-96.74189800000001</v>
+        <v>-122.308998</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>Sioux Falls, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12898,35 +12898,35 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>Sioux Falls</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>13.0746</v>
+        <v>43.582001</v>
       </c>
       <c r="H333" t="n">
-        <v>-59.4925</v>
+        <v>-96.74189800000001</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>St. Louis, United States</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12936,35 +12936,35 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>38.748699</v>
+        <v>13.0746</v>
       </c>
       <c r="H334" t="n">
-        <v>-90.370003</v>
+        <v>-59.4925</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tallahassee, United States</t>
+          <t>St. Louis, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Tallahassee</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -12988,21 +12988,21 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>30.3965</v>
+        <v>38.748699</v>
       </c>
       <c r="H335" t="n">
-        <v>-84.35030399999999</v>
+        <v>-90.370003</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>Tallahassee, United States</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13012,35 +13012,35 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Tallahassee</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>19.406099</v>
+        <v>30.3965</v>
       </c>
       <c r="H336" t="n">
-        <v>-70.604698</v>
+        <v>-84.35030399999999</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tampa, United States</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13050,35 +13050,35 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>27.9755</v>
+        <v>19.406099</v>
       </c>
       <c r="H337" t="n">
-        <v>-82.533203</v>
+        <v>-70.604698</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Toronto, Canada</t>
+          <t>Tampa, United States</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13088,35 +13088,35 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>43.6772</v>
+        <v>27.9755</v>
       </c>
       <c r="H338" t="n">
-        <v>-79.6306</v>
+        <v>-82.533203</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Vancouver, Canada</t>
+          <t>Toronto, Canada</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -13140,21 +13140,21 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>49.193901</v>
+        <v>43.6772</v>
       </c>
       <c r="H339" t="n">
-        <v>-123.183998</v>
+        <v>-79.6306</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>Vancouver, Canada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13164,35 +13164,35 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>18.4394</v>
+        <v>49.193901</v>
       </c>
       <c r="H340" t="n">
-        <v>-66.001801</v>
+        <v>-123.183998</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Winnipeg, Canada</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13202,61 +13202,99 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Winnipeg</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>49.91</v>
+        <v>18.4394</v>
       </c>
       <c r="H341" t="n">
-        <v>-97.23989899999999</v>
+        <v>-66.001801</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
+          <t>YWG</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Winnipeg, Canada</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="H342" t="n">
+        <v>-97.23989899999999</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
           <t>CVG</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>Cincinnati, United States</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C343" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D343" t="inlineStr">
         <is>
           <t>Hebron</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
+      <c r="E343" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
+      <c r="F343" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G342" t="n">
+      <c r="G343" t="n">
         <v>39.048801</v>
       </c>
-      <c r="H342" t="n">
+      <c r="H343" t="n">
         <v>-84.667801</v>
       </c>
     </row>
